--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5652.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5652.xlsx
@@ -1414,6 +1414,18 @@
       <c r="E14" t="n">
         <v>1.23</v>
       </c>
+      <c r="G14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7</v>
+      </c>
       <c r="K14" t="n">
         <v>0.84</v>
       </c>
@@ -1438,12 +1450,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-08-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-08-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-08-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-08-08-08-08-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-08-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-08-08-08-08-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL4@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1738,6 +1750,18 @@
       <c r="E18" t="n">
         <v>2.08</v>
       </c>
+      <c r="G18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.72</v>
+      </c>
       <c r="K18" t="n">
         <v>1.9</v>
       </c>
@@ -1762,12 +1786,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-24-24-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-24-24-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-24-24-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-24-24-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-24-24-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-24-24-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL4@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1792,6 +1816,18 @@
           <t>5652-32-32-32-32-FG</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.2</v>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>5652-32-32-32-32-FG</t>
@@ -1804,12 +1840,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL4@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5652.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5652.xlsx
@@ -1414,6 +1414,9 @@
       <c r="E14" t="n">
         <v>1.23</v>
       </c>
+      <c r="F14" t="n">
+        <v>1.062</v>
+      </c>
       <c r="G14" t="n">
         <v>0.7</v>
       </c>
@@ -1445,17 +1448,17 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-08-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE, W@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-08-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-08-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-08-08-08-08-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL4@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-08-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-08-08-08-08-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD, W@HEX=Y; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -08 0.7 (A1) | TAPDRILL4@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1750,6 +1753,9 @@
       <c r="E18" t="n">
         <v>2.08</v>
       </c>
+      <c r="F18" t="n">
+        <v>2.561</v>
+      </c>
       <c r="G18" t="n">
         <v>1.72</v>
       </c>
@@ -1781,17 +1787,17 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-24-24-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL4@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, N1_3@DRIVE, N1_4@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, THDMAJ_A4@DRIVE, W@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5652-24-24-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-24-24-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-24-24-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL4@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5652-24-24-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5652-24-24-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N, N1_3@DRIVE=N, N1_4@DRIVE=N, THDMAJ_A1@DRIVE=B1THD, THDMAJ_A2@DRIVE=B1THD, THDMAJ_A3@DRIVE=B1THD, THDMAJ_A4@DRIVE=B1THD, W@HEX=Y; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL4@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
